--- a/pages/Base_de_Donnees_Ventes.xlsx
+++ b/pages/Base_de_Donnees_Ventes.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Demand_Forecasting_System-main\Demand_Forecasting_System-main\pages\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Demand_Forecasting_System-main\Demand_Forecasting_System-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10785" windowHeight="3195"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7313"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,82 +45,10 @@
     <t>Yearly_Stock</t>
   </si>
   <si>
-    <t>2021-01</t>
+    <t>2023-01</t>
   </si>
   <si>
     <t>Lait</t>
-  </si>
-  <si>
-    <t>2021-02</t>
-  </si>
-  <si>
-    <t>2021-03</t>
-  </si>
-  <si>
-    <t>2021-04</t>
-  </si>
-  <si>
-    <t>2021-05</t>
-  </si>
-  <si>
-    <t>2021-06</t>
-  </si>
-  <si>
-    <t>2021-07</t>
-  </si>
-  <si>
-    <t>2021-08</t>
-  </si>
-  <si>
-    <t>2021-09</t>
-  </si>
-  <si>
-    <t>2021-10</t>
-  </si>
-  <si>
-    <t>2021-11</t>
-  </si>
-  <si>
-    <t>2021-12</t>
-  </si>
-  <si>
-    <t>2022-01</t>
-  </si>
-  <si>
-    <t>2022-02</t>
-  </si>
-  <si>
-    <t>2022-03</t>
-  </si>
-  <si>
-    <t>2022-04</t>
-  </si>
-  <si>
-    <t>2022-05</t>
-  </si>
-  <si>
-    <t>2022-06</t>
-  </si>
-  <si>
-    <t>2022-07</t>
-  </si>
-  <si>
-    <t>2022-08</t>
-  </si>
-  <si>
-    <t>2022-09</t>
-  </si>
-  <si>
-    <t>2022-10</t>
-  </si>
-  <si>
-    <t>2022-11</t>
-  </si>
-  <si>
-    <t>2022-12</t>
-  </si>
-  <si>
-    <t>2023-01</t>
   </si>
   <si>
     <t>2023-02</t>
@@ -154,6 +82,78 @@
   </si>
   <si>
     <t>2023-12</t>
+  </si>
+  <si>
+    <t>2024-01</t>
+  </si>
+  <si>
+    <t>2024-02</t>
+  </si>
+  <si>
+    <t>2024-03</t>
+  </si>
+  <si>
+    <t>2024-04</t>
+  </si>
+  <si>
+    <t>2024-05</t>
+  </si>
+  <si>
+    <t>2024-06</t>
+  </si>
+  <si>
+    <t>2024-07</t>
+  </si>
+  <si>
+    <t>2024-08</t>
+  </si>
+  <si>
+    <t>2024-09</t>
+  </si>
+  <si>
+    <t>2024-10</t>
+  </si>
+  <si>
+    <t>2024-11</t>
+  </si>
+  <si>
+    <t>2024-12</t>
+  </si>
+  <si>
+    <t>2025-01</t>
+  </si>
+  <si>
+    <t>2025-02</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>2025-04</t>
+  </si>
+  <si>
+    <t>2025-05</t>
+  </si>
+  <si>
+    <t>2025-06</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
   </si>
   <si>
     <t>Café</t>
@@ -538,13 +538,9 @@
   <dimension ref="A1:H541"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.46484375" customWidth="1"/>
-    <col min="2" max="2" width="17.73046875" customWidth="1"/>
-    <col min="3" max="3" width="13.73046875" customWidth="1"/>
-    <col min="4" max="4" width="14.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" customWidth="1"/>
-    <col min="7" max="7" width="12.796875" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="4" max="4" width="15.46484375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -590,7 +586,7 @@
         <v>223</v>
       </c>
       <c r="F2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G2">
         <v>4476</v>
@@ -616,7 +612,7 @@
         <v>453</v>
       </c>
       <c r="F3">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G3">
         <v>5076</v>
@@ -642,7 +638,7 @@
         <v>254</v>
       </c>
       <c r="F4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G4">
         <v>1764</v>
@@ -668,7 +664,7 @@
         <v>406</v>
       </c>
       <c r="F5">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G5">
         <v>5172</v>
@@ -694,7 +690,7 @@
         <v>394</v>
       </c>
       <c r="F6">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G6">
         <v>3660</v>
@@ -720,7 +716,7 @@
         <v>368</v>
       </c>
       <c r="F7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G7">
         <v>2004</v>
@@ -746,7 +742,7 @@
         <v>487</v>
       </c>
       <c r="F8">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G8">
         <v>1212</v>
@@ -772,7 +768,7 @@
         <v>251</v>
       </c>
       <c r="F9">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G9">
         <v>876</v>
@@ -798,7 +794,7 @@
         <v>524</v>
       </c>
       <c r="F10">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G10">
         <v>5340</v>
@@ -824,7 +820,7 @@
         <v>260</v>
       </c>
       <c r="F11">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G11">
         <v>2160</v>
@@ -850,7 +846,7 @@
         <v>270</v>
       </c>
       <c r="F12">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G12">
         <v>2652</v>
@@ -876,7 +872,7 @@
         <v>546</v>
       </c>
       <c r="F13">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G13">
         <v>1836</v>
@@ -902,7 +898,7 @@
         <v>409</v>
       </c>
       <c r="F14">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G14">
         <v>3396</v>
@@ -928,7 +924,7 @@
         <v>588</v>
       </c>
       <c r="F15">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G15">
         <v>2640</v>
@@ -954,7 +950,7 @@
         <v>561</v>
       </c>
       <c r="F16">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G16">
         <v>4056</v>
@@ -980,7 +976,7 @@
         <v>530</v>
       </c>
       <c r="F17">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G17">
         <v>2508</v>
@@ -1006,7 +1002,7 @@
         <v>406</v>
       </c>
       <c r="F18">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G18">
         <v>2232</v>
@@ -1032,7 +1028,7 @@
         <v>334</v>
       </c>
       <c r="F19">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G19">
         <v>4596</v>
@@ -1058,7 +1054,7 @@
         <v>488</v>
       </c>
       <c r="F20">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G20">
         <v>3036</v>
@@ -1084,7 +1080,7 @@
         <v>595</v>
       </c>
       <c r="F21">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G21">
         <v>1908</v>
@@ -1110,7 +1106,7 @@
         <v>308</v>
       </c>
       <c r="F22">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G22">
         <v>2544</v>
@@ -1136,7 +1132,7 @@
         <v>570</v>
       </c>
       <c r="F23">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G23">
         <v>4524</v>
@@ -1162,7 +1158,7 @@
         <v>460</v>
       </c>
       <c r="F24">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G24">
         <v>1512</v>
@@ -1188,7 +1184,7 @@
         <v>561</v>
       </c>
       <c r="F25">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G25">
         <v>3396</v>
@@ -1214,7 +1210,7 @@
         <v>248</v>
       </c>
       <c r="F26">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G26">
         <v>2593</v>
@@ -1240,7 +1236,7 @@
         <v>386</v>
       </c>
       <c r="F27">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G27">
         <v>2593</v>
@@ -1266,7 +1262,7 @@
         <v>336</v>
       </c>
       <c r="F28">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G28">
         <v>2593</v>
@@ -1292,7 +1288,7 @@
         <v>573</v>
       </c>
       <c r="F29">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G29">
         <v>2593</v>
@@ -1318,7 +1314,7 @@
         <v>323</v>
       </c>
       <c r="F30">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G30">
         <v>2593</v>
@@ -1344,7 +1340,7 @@
         <v>216</v>
       </c>
       <c r="F31">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G31">
         <v>2593</v>
@@ -1370,7 +1366,7 @@
         <v>385</v>
       </c>
       <c r="F32">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G32">
         <v>2593</v>
@@ -1396,7 +1392,7 @@
         <v>422</v>
       </c>
       <c r="F33">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G33">
         <v>2593</v>
@@ -1422,7 +1418,7 @@
         <v>150</v>
       </c>
       <c r="F34">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G34">
         <v>2593</v>
@@ -1448,7 +1444,7 @@
         <v>400</v>
       </c>
       <c r="F35">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G35">
         <v>2593</v>
@@ -1474,7 +1470,7 @@
         <v>353</v>
       </c>
       <c r="F36">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G36">
         <v>2593</v>
@@ -1500,7 +1496,7 @@
         <v>363</v>
       </c>
       <c r="F37">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G37">
         <v>2593</v>
@@ -1526,7 +1522,7 @@
         <v>338</v>
       </c>
       <c r="F38">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G38">
         <v>3060</v>
@@ -1552,7 +1548,7 @@
         <v>260</v>
       </c>
       <c r="F39">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G39">
         <v>4080</v>
@@ -1578,7 +1574,7 @@
         <v>590</v>
       </c>
       <c r="F40">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G40">
         <v>1260</v>
@@ -1604,7 +1600,7 @@
         <v>343</v>
       </c>
       <c r="F41">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G41">
         <v>2052</v>
@@ -1630,7 +1626,7 @@
         <v>389</v>
       </c>
       <c r="F42">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G42">
         <v>3492</v>
@@ -1656,7 +1652,7 @@
         <v>224</v>
       </c>
       <c r="F43">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G43">
         <v>3144</v>
@@ -1682,7 +1678,7 @@
         <v>385</v>
       </c>
       <c r="F44">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G44">
         <v>3636</v>
@@ -1708,7 +1704,7 @@
         <v>391</v>
       </c>
       <c r="F45">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G45">
         <v>5664</v>
@@ -1734,7 +1730,7 @@
         <v>549</v>
       </c>
       <c r="F46">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G46">
         <v>1056</v>
@@ -1760,7 +1756,7 @@
         <v>550</v>
       </c>
       <c r="F47">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G47">
         <v>5856</v>
@@ -1786,7 +1782,7 @@
         <v>462</v>
       </c>
       <c r="F48">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G48">
         <v>1788</v>
@@ -1812,7 +1808,7 @@
         <v>314</v>
       </c>
       <c r="F49">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G49">
         <v>4392</v>
@@ -1838,7 +1834,7 @@
         <v>360</v>
       </c>
       <c r="F50">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G50">
         <v>1464</v>
@@ -1864,7 +1860,7 @@
         <v>463</v>
       </c>
       <c r="F51">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G51">
         <v>3792</v>
@@ -1890,7 +1886,7 @@
         <v>511</v>
       </c>
       <c r="F52">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G52">
         <v>612</v>
@@ -1916,7 +1912,7 @@
         <v>317</v>
       </c>
       <c r="F53">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G53">
         <v>3540</v>
@@ -1942,7 +1938,7 @@
         <v>429</v>
       </c>
       <c r="F54">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G54">
         <v>2880</v>
@@ -1968,7 +1964,7 @@
         <v>267</v>
       </c>
       <c r="F55">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G55">
         <v>5376</v>
@@ -1994,7 +1990,7 @@
         <v>518</v>
       </c>
       <c r="F56">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G56">
         <v>3168</v>
@@ -2020,7 +2016,7 @@
         <v>272</v>
       </c>
       <c r="F57">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G57">
         <v>4692</v>
@@ -2046,7 +2042,7 @@
         <v>225</v>
       </c>
       <c r="F58">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G58">
         <v>3588</v>
@@ -2072,7 +2068,7 @@
         <v>587</v>
       </c>
       <c r="F59">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G59">
         <v>3864</v>
@@ -2098,7 +2094,7 @@
         <v>375</v>
       </c>
       <c r="F60">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G60">
         <v>744</v>
@@ -2124,7 +2120,7 @@
         <v>561</v>
       </c>
       <c r="F61">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G61">
         <v>5280</v>
@@ -2150,7 +2146,7 @@
         <v>142</v>
       </c>
       <c r="F62">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G62">
         <v>2811</v>
@@ -2176,7 +2172,7 @@
         <v>426</v>
       </c>
       <c r="F63">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G63">
         <v>2811</v>
@@ -2202,7 +2198,7 @@
         <v>312</v>
       </c>
       <c r="F64">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G64">
         <v>2811</v>
@@ -2228,7 +2224,7 @@
         <v>353</v>
       </c>
       <c r="F65">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G65">
         <v>2811</v>
@@ -2254,7 +2250,7 @@
         <v>351</v>
       </c>
       <c r="F66">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G66">
         <v>2811</v>
@@ -2280,7 +2276,7 @@
         <v>265</v>
       </c>
       <c r="F67">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G67">
         <v>2811</v>
@@ -2306,7 +2302,7 @@
         <v>380</v>
       </c>
       <c r="F68">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G68">
         <v>2811</v>
@@ -2332,7 +2328,7 @@
         <v>500</v>
       </c>
       <c r="F69">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G69">
         <v>2811</v>
@@ -2358,7 +2354,7 @@
         <v>382</v>
       </c>
       <c r="F70">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G70">
         <v>2811</v>
@@ -2384,7 +2380,7 @@
         <v>387</v>
       </c>
       <c r="F71">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G71">
         <v>2811</v>
@@ -2410,7 +2406,7 @@
         <v>557</v>
       </c>
       <c r="F72">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G72">
         <v>2811</v>
@@ -2436,7 +2432,7 @@
         <v>337</v>
       </c>
       <c r="F73">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G73">
         <v>2811</v>
@@ -2462,7 +2458,7 @@
         <v>239</v>
       </c>
       <c r="F74">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G74">
         <v>4560</v>
@@ -2488,7 +2484,7 @@
         <v>374</v>
       </c>
       <c r="F75">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G75">
         <v>4596</v>
@@ -2514,7 +2510,7 @@
         <v>272</v>
       </c>
       <c r="F76">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G76">
         <v>2016</v>
@@ -2540,7 +2536,7 @@
         <v>421</v>
       </c>
       <c r="F77">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G77">
         <v>876</v>
@@ -2566,7 +2562,7 @@
         <v>506</v>
       </c>
       <c r="F78">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G78">
         <v>3384</v>
@@ -2592,7 +2588,7 @@
         <v>356</v>
       </c>
       <c r="F79">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G79">
         <v>4344</v>
@@ -2618,7 +2614,7 @@
         <v>222</v>
       </c>
       <c r="F80">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G80">
         <v>4632</v>
@@ -2644,7 +2640,7 @@
         <v>293</v>
       </c>
       <c r="F81">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G81">
         <v>3876</v>
@@ -2670,7 +2666,7 @@
         <v>315</v>
       </c>
       <c r="F82">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G82">
         <v>612</v>
@@ -2696,7 +2692,7 @@
         <v>542</v>
       </c>
       <c r="F83">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G83">
         <v>5424</v>
@@ -2722,7 +2718,7 @@
         <v>317</v>
       </c>
       <c r="F84">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G84">
         <v>660</v>
@@ -2748,7 +2744,7 @@
         <v>420</v>
       </c>
       <c r="F85">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G85">
         <v>4092</v>
@@ -2774,7 +2770,7 @@
         <v>365</v>
       </c>
       <c r="F86">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G86">
         <v>1860</v>
@@ -2800,7 +2796,7 @@
         <v>348</v>
       </c>
       <c r="F87">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G87">
         <v>5952</v>
@@ -2826,7 +2822,7 @@
         <v>414</v>
       </c>
       <c r="F88">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G88">
         <v>5544</v>
@@ -2852,7 +2848,7 @@
         <v>258</v>
       </c>
       <c r="F89">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G89">
         <v>4728</v>
@@ -2878,7 +2874,7 @@
         <v>463</v>
       </c>
       <c r="F90">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G90">
         <v>2484</v>
@@ -2904,7 +2900,7 @@
         <v>211</v>
       </c>
       <c r="F91">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G91">
         <v>4032</v>
@@ -2930,7 +2926,7 @@
         <v>569</v>
       </c>
       <c r="F92">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G92">
         <v>5772</v>
@@ -2956,7 +2952,7 @@
         <v>233</v>
       </c>
       <c r="F93">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G93">
         <v>2160</v>
@@ -2982,7 +2978,7 @@
         <v>370</v>
       </c>
       <c r="F94">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G94">
         <v>4044</v>
@@ -3008,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="F95">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G95">
         <v>1056</v>
@@ -3034,7 +3030,7 @@
         <v>544</v>
       </c>
       <c r="F96">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G96">
         <v>2652</v>
@@ -3060,7 +3056,7 @@
         <v>216</v>
       </c>
       <c r="F97">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G97">
         <v>5304</v>
@@ -3086,7 +3082,7 @@
         <v>305</v>
       </c>
       <c r="F98">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G98">
         <v>3096</v>
@@ -3112,7 +3108,7 @@
         <v>393</v>
       </c>
       <c r="F99">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G99">
         <v>3096</v>
@@ -3138,7 +3134,7 @@
         <v>400</v>
       </c>
       <c r="F100">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G100">
         <v>3096</v>
@@ -3164,7 +3160,7 @@
         <v>333</v>
       </c>
       <c r="F101">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G101">
         <v>3096</v>
@@ -3190,7 +3186,7 @@
         <v>470</v>
       </c>
       <c r="F102">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G102">
         <v>3096</v>
@@ -3216,7 +3212,7 @@
         <v>362</v>
       </c>
       <c r="F103">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G103">
         <v>3096</v>
@@ -3242,7 +3238,7 @@
         <v>421</v>
       </c>
       <c r="F104">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G104">
         <v>3096</v>
@@ -3268,7 +3264,7 @@
         <v>304</v>
       </c>
       <c r="F105">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G105">
         <v>3096</v>
@@ -3294,7 +3290,7 @@
         <v>170</v>
       </c>
       <c r="F106">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G106">
         <v>3096</v>
@@ -3320,7 +3316,7 @@
         <v>164</v>
       </c>
       <c r="F107">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G107">
         <v>3096</v>
@@ -3346,7 +3342,7 @@
         <v>391</v>
       </c>
       <c r="F108">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G108">
         <v>3096</v>
@@ -3372,7 +3368,7 @@
         <v>218</v>
       </c>
       <c r="F109">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G109">
         <v>3096</v>
@@ -3398,7 +3394,7 @@
         <v>333</v>
       </c>
       <c r="F110">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G110">
         <v>4032</v>
@@ -3424,7 +3420,7 @@
         <v>397</v>
       </c>
       <c r="F111">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G111">
         <v>840</v>
@@ -3450,7 +3446,7 @@
         <v>410</v>
       </c>
       <c r="F112">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G112">
         <v>1992</v>
@@ -3476,7 +3472,7 @@
         <v>382</v>
       </c>
       <c r="F113">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G113">
         <v>1884</v>
@@ -3502,7 +3498,7 @@
         <v>255</v>
       </c>
       <c r="F114">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G114">
         <v>1368</v>
@@ -3528,7 +3524,7 @@
         <v>541</v>
       </c>
       <c r="F115">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G115">
         <v>2952</v>
@@ -3554,7 +3550,7 @@
         <v>213</v>
       </c>
       <c r="F116">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G116">
         <v>4500</v>
@@ -3580,7 +3576,7 @@
         <v>475</v>
       </c>
       <c r="F117">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G117">
         <v>2892</v>
@@ -3606,7 +3602,7 @@
         <v>275</v>
       </c>
       <c r="F118">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G118">
         <v>3432</v>
@@ -3632,7 +3628,7 @@
         <v>205</v>
       </c>
       <c r="F119">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G119">
         <v>1416</v>
@@ -3658,7 +3654,7 @@
         <v>422</v>
       </c>
       <c r="F120">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G120">
         <v>5928</v>
@@ -3684,7 +3680,7 @@
         <v>230</v>
       </c>
       <c r="F121">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G121">
         <v>2796</v>
@@ -3710,7 +3706,7 @@
         <v>306</v>
       </c>
       <c r="F122">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G122">
         <v>4236</v>
@@ -3736,7 +3732,7 @@
         <v>338</v>
       </c>
       <c r="F123">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G123">
         <v>2424</v>
@@ -3762,7 +3758,7 @@
         <v>407</v>
       </c>
       <c r="F124">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G124">
         <v>1800</v>
@@ -3788,7 +3784,7 @@
         <v>358</v>
       </c>
       <c r="F125">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G125">
         <v>4632</v>
@@ -3814,7 +3810,7 @@
         <v>599</v>
       </c>
       <c r="F126">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G126">
         <v>1104</v>
@@ -3840,7 +3836,7 @@
         <v>203</v>
       </c>
       <c r="F127">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G127">
         <v>1692</v>
@@ -3866,7 +3862,7 @@
         <v>510</v>
       </c>
       <c r="F128">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G128">
         <v>3636</v>
@@ -3892,7 +3888,7 @@
         <v>460</v>
       </c>
       <c r="F129">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G129">
         <v>3372</v>
@@ -3918,7 +3914,7 @@
         <v>322</v>
       </c>
       <c r="F130">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G130">
         <v>5436</v>
@@ -3944,7 +3940,7 @@
         <v>568</v>
       </c>
       <c r="F131">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G131">
         <v>3720</v>
@@ -3970,7 +3966,7 @@
         <v>459</v>
       </c>
       <c r="F132">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G132">
         <v>2916</v>
@@ -3996,7 +3992,7 @@
         <v>350</v>
       </c>
       <c r="F133">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G133">
         <v>2976</v>
@@ -4022,7 +4018,7 @@
         <v>298</v>
       </c>
       <c r="F134">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G134">
         <v>2382</v>
@@ -4048,7 +4044,7 @@
         <v>430</v>
       </c>
       <c r="F135">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G135">
         <v>2382</v>
@@ -4074,7 +4070,7 @@
         <v>446</v>
       </c>
       <c r="F136">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G136">
         <v>2382</v>
@@ -4100,7 +4096,7 @@
         <v>357</v>
       </c>
       <c r="F137">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G137">
         <v>2382</v>
@@ -4126,7 +4122,7 @@
         <v>357</v>
       </c>
       <c r="F138">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G138">
         <v>2382</v>
@@ -4152,7 +4148,7 @@
         <v>500</v>
       </c>
       <c r="F139">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G139">
         <v>2382</v>
@@ -4178,7 +4174,7 @@
         <v>583</v>
       </c>
       <c r="F140">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G140">
         <v>2382</v>
@@ -4204,7 +4200,7 @@
         <v>430</v>
       </c>
       <c r="F141">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G141">
         <v>2382</v>
@@ -4230,7 +4226,7 @@
         <v>548</v>
       </c>
       <c r="F142">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G142">
         <v>2382</v>
@@ -4256,7 +4252,7 @@
         <v>463</v>
       </c>
       <c r="F143">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G143">
         <v>2382</v>
@@ -4282,7 +4278,7 @@
         <v>403</v>
       </c>
       <c r="F144">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G144">
         <v>2382</v>
@@ -4308,7 +4304,7 @@
         <v>524</v>
       </c>
       <c r="F145">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G145">
         <v>2382</v>
@@ -4334,7 +4330,7 @@
         <v>219</v>
       </c>
       <c r="F146">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G146">
         <v>5928</v>
@@ -4360,7 +4356,7 @@
         <v>384</v>
       </c>
       <c r="F147">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G147">
         <v>4596</v>
@@ -4386,7 +4382,7 @@
         <v>406</v>
       </c>
       <c r="F148">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G148">
         <v>2916</v>
@@ -4412,7 +4408,7 @@
         <v>276</v>
       </c>
       <c r="F149">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G149">
         <v>4608</v>
@@ -4438,7 +4434,7 @@
         <v>283</v>
       </c>
       <c r="F150">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G150">
         <v>3792</v>
@@ -4464,7 +4460,7 @@
         <v>318</v>
       </c>
       <c r="F151">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G151">
         <v>4344</v>
@@ -4490,7 +4486,7 @@
         <v>478</v>
       </c>
       <c r="F152">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G152">
         <v>5748</v>
@@ -4516,7 +4512,7 @@
         <v>531</v>
       </c>
       <c r="F153">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G153">
         <v>3804</v>
@@ -4542,7 +4538,7 @@
         <v>240</v>
       </c>
       <c r="F154">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G154">
         <v>2880</v>
@@ -4568,7 +4564,7 @@
         <v>370</v>
       </c>
       <c r="F155">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G155">
         <v>3480</v>
@@ -4594,7 +4590,7 @@
         <v>525</v>
       </c>
       <c r="F156">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G156">
         <v>5724</v>
@@ -4620,7 +4616,7 @@
         <v>493</v>
       </c>
       <c r="F157">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G157">
         <v>4344</v>
@@ -4646,7 +4642,7 @@
         <v>320</v>
       </c>
       <c r="F158">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G158">
         <v>648</v>
@@ -4672,7 +4668,7 @@
         <v>549</v>
       </c>
       <c r="F159">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G159">
         <v>3372</v>
@@ -4698,7 +4694,7 @@
         <v>582</v>
       </c>
       <c r="F160">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G160">
         <v>4572</v>
@@ -4724,7 +4720,7 @@
         <v>567</v>
       </c>
       <c r="F161">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G161">
         <v>4212</v>
@@ -4750,7 +4746,7 @@
         <v>425</v>
       </c>
       <c r="F162">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G162">
         <v>3708</v>
@@ -4776,7 +4772,7 @@
         <v>586</v>
       </c>
       <c r="F163">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G163">
         <v>4596</v>
@@ -4802,7 +4798,7 @@
         <v>363</v>
       </c>
       <c r="F164">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G164">
         <v>4884</v>
@@ -4828,7 +4824,7 @@
         <v>352</v>
       </c>
       <c r="F165">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G165">
         <v>2052</v>
@@ -4854,7 +4850,7 @@
         <v>485</v>
       </c>
       <c r="F166">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G166">
         <v>3288</v>
@@ -4880,7 +4876,7 @@
         <v>394</v>
       </c>
       <c r="F167">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G167">
         <v>3540</v>
@@ -4906,7 +4902,7 @@
         <v>364</v>
       </c>
       <c r="F168">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G168">
         <v>5016</v>
@@ -4932,7 +4928,7 @@
         <v>435</v>
       </c>
       <c r="F169">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G169">
         <v>1008</v>
@@ -4958,7 +4954,7 @@
         <v>435</v>
       </c>
       <c r="F170">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G170">
         <v>2861</v>
@@ -4984,7 +4980,7 @@
         <v>243</v>
       </c>
       <c r="F171">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G171">
         <v>2861</v>
@@ -5010,7 +5006,7 @@
         <v>423</v>
       </c>
       <c r="F172">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G172">
         <v>2861</v>
@@ -5036,7 +5032,7 @@
         <v>364</v>
       </c>
       <c r="F173">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G173">
         <v>2861</v>
@@ -5062,7 +5058,7 @@
         <v>293</v>
       </c>
       <c r="F174">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G174">
         <v>2861</v>
@@ -5088,7 +5084,7 @@
         <v>186</v>
       </c>
       <c r="F175">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G175">
         <v>2861</v>
@@ -5114,7 +5110,7 @@
         <v>282</v>
       </c>
       <c r="F176">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G176">
         <v>2861</v>
@@ -5140,7 +5136,7 @@
         <v>265</v>
       </c>
       <c r="F177">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G177">
         <v>2861</v>
@@ -5166,7 +5162,7 @@
         <v>264</v>
       </c>
       <c r="F178">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G178">
         <v>2861</v>
@@ -5192,7 +5188,7 @@
         <v>268</v>
       </c>
       <c r="F179">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G179">
         <v>2861</v>
@@ -5218,7 +5214,7 @@
         <v>355</v>
       </c>
       <c r="F180">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G180">
         <v>2861</v>
@@ -5244,7 +5240,7 @@
         <v>414</v>
       </c>
       <c r="F181">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G181">
         <v>2861</v>
@@ -5270,7 +5266,7 @@
         <v>476</v>
       </c>
       <c r="F182">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G182">
         <v>5628</v>
@@ -5296,7 +5292,7 @@
         <v>282</v>
       </c>
       <c r="F183">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G183">
         <v>3732</v>
@@ -5322,7 +5318,7 @@
         <v>353</v>
       </c>
       <c r="F184">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G184">
         <v>1260</v>
@@ -5348,7 +5344,7 @@
         <v>419</v>
       </c>
       <c r="F185">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G185">
         <v>3564</v>
@@ -5374,7 +5370,7 @@
         <v>219</v>
       </c>
       <c r="F186">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G186">
         <v>4944</v>
@@ -5400,7 +5396,7 @@
         <v>462</v>
       </c>
       <c r="F187">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G187">
         <v>4104</v>
@@ -5426,7 +5422,7 @@
         <v>298</v>
       </c>
       <c r="F188">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G188">
         <v>3420</v>
@@ -5452,7 +5448,7 @@
         <v>326</v>
       </c>
       <c r="F189">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G189">
         <v>5436</v>
@@ -5478,7 +5474,7 @@
         <v>243</v>
       </c>
       <c r="F190">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G190">
         <v>828</v>
@@ -5504,7 +5500,7 @@
         <v>431</v>
       </c>
       <c r="F191">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G191">
         <v>1848</v>
@@ -5530,7 +5526,7 @@
         <v>291</v>
       </c>
       <c r="F192">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G192">
         <v>2952</v>
@@ -5556,7 +5552,7 @@
         <v>292</v>
       </c>
       <c r="F193">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G193">
         <v>5352</v>
@@ -5582,7 +5578,7 @@
         <v>590</v>
       </c>
       <c r="F194">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G194">
         <v>5604</v>
@@ -5608,7 +5604,7 @@
         <v>450</v>
       </c>
       <c r="F195">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G195">
         <v>4488</v>
@@ -5634,7 +5630,7 @@
         <v>419</v>
       </c>
       <c r="F196">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G196">
         <v>3192</v>
@@ -5660,7 +5656,7 @@
         <v>278</v>
       </c>
       <c r="F197">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G197">
         <v>3372</v>
@@ -5686,7 +5682,7 @@
         <v>403</v>
       </c>
       <c r="F198">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G198">
         <v>3324</v>
@@ -5712,7 +5708,7 @@
         <v>289</v>
       </c>
       <c r="F199">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G199">
         <v>1836</v>
@@ -5738,7 +5734,7 @@
         <v>304</v>
       </c>
       <c r="F200">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G200">
         <v>2112</v>
@@ -5764,7 +5760,7 @@
         <v>238</v>
       </c>
       <c r="F201">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G201">
         <v>3372</v>
@@ -5790,7 +5786,7 @@
         <v>430</v>
       </c>
       <c r="F202">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G202">
         <v>624</v>
@@ -5816,7 +5812,7 @@
         <v>585</v>
       </c>
       <c r="F203">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G203">
         <v>1128</v>
@@ -5842,7 +5838,7 @@
         <v>597</v>
       </c>
       <c r="F204">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G204">
         <v>2172</v>
@@ -5868,7 +5864,7 @@
         <v>592</v>
       </c>
       <c r="F205">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G205">
         <v>4032</v>
@@ -5894,7 +5890,7 @@
         <v>251</v>
       </c>
       <c r="F206">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G206">
         <v>2431</v>
@@ -5920,7 +5916,7 @@
         <v>167</v>
       </c>
       <c r="F207">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G207">
         <v>2431</v>
@@ -5946,7 +5942,7 @@
         <v>289</v>
       </c>
       <c r="F208">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G208">
         <v>2431</v>
@@ -5972,7 +5968,7 @@
         <v>371</v>
       </c>
       <c r="F209">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G209">
         <v>2431</v>
@@ -5998,7 +5994,7 @@
         <v>328</v>
       </c>
       <c r="F210">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G210">
         <v>2431</v>
@@ -6024,7 +6020,7 @@
         <v>310</v>
       </c>
       <c r="F211">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G211">
         <v>2431</v>
@@ -6050,7 +6046,7 @@
         <v>194</v>
       </c>
       <c r="F212">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G212">
         <v>2431</v>
@@ -6076,7 +6072,7 @@
         <v>350</v>
       </c>
       <c r="F213">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G213">
         <v>2431</v>
@@ -6102,7 +6098,7 @@
         <v>151</v>
       </c>
       <c r="F214">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G214">
         <v>2431</v>
@@ -6128,7 +6124,7 @@
         <v>173</v>
       </c>
       <c r="F215">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G215">
         <v>2431</v>
@@ -6154,7 +6150,7 @@
         <v>317</v>
       </c>
       <c r="F216">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G216">
         <v>2431</v>
@@ -6180,7 +6176,7 @@
         <v>365</v>
       </c>
       <c r="F217">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G217">
         <v>2431</v>
@@ -6206,7 +6202,7 @@
         <v>590</v>
       </c>
       <c r="F218">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G218">
         <v>2208</v>
@@ -6232,7 +6228,7 @@
         <v>466</v>
       </c>
       <c r="F219">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G219">
         <v>4548</v>
@@ -6258,7 +6254,7 @@
         <v>350</v>
       </c>
       <c r="F220">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G220">
         <v>5088</v>
@@ -6284,7 +6280,7 @@
         <v>435</v>
       </c>
       <c r="F221">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G221">
         <v>1116</v>
@@ -6310,7 +6306,7 @@
         <v>362</v>
       </c>
       <c r="F222">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G222">
         <v>2628</v>
@@ -6336,7 +6332,7 @@
         <v>227</v>
       </c>
       <c r="F223">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G223">
         <v>1980</v>
@@ -6362,7 +6358,7 @@
         <v>599</v>
       </c>
       <c r="F224">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G224">
         <v>5544</v>
@@ -6388,7 +6384,7 @@
         <v>357</v>
       </c>
       <c r="F225">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G225">
         <v>3984</v>
@@ -6414,7 +6410,7 @@
         <v>343</v>
       </c>
       <c r="F226">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G226">
         <v>1944</v>
@@ -6440,7 +6436,7 @@
         <v>484</v>
       </c>
       <c r="F227">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G227">
         <v>3660</v>
@@ -6466,7 +6462,7 @@
         <v>400</v>
       </c>
       <c r="F228">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G228">
         <v>5352</v>
@@ -6492,7 +6488,7 @@
         <v>397</v>
       </c>
       <c r="F229">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G229">
         <v>2352</v>
@@ -6518,7 +6514,7 @@
         <v>344</v>
       </c>
       <c r="F230">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G230">
         <v>5316</v>
@@ -6544,7 +6540,7 @@
         <v>469</v>
       </c>
       <c r="F231">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G231">
         <v>1896</v>
@@ -6570,7 +6566,7 @@
         <v>442</v>
       </c>
       <c r="F232">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G232">
         <v>2292</v>
@@ -6596,7 +6592,7 @@
         <v>401</v>
       </c>
       <c r="F233">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G233">
         <v>3852</v>
@@ -6622,7 +6618,7 @@
         <v>529</v>
       </c>
       <c r="F234">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G234">
         <v>3792</v>
@@ -6648,7 +6644,7 @@
         <v>279</v>
       </c>
       <c r="F235">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G235">
         <v>852</v>
@@ -6674,7 +6670,7 @@
         <v>276</v>
       </c>
       <c r="F236">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G236">
         <v>2052</v>
@@ -6700,7 +6696,7 @@
         <v>348</v>
       </c>
       <c r="F237">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G237">
         <v>5400</v>
@@ -6726,7 +6722,7 @@
         <v>387</v>
       </c>
       <c r="F238">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G238">
         <v>4248</v>
@@ -6752,7 +6748,7 @@
         <v>586</v>
       </c>
       <c r="F239">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G239">
         <v>5700</v>
@@ -6778,7 +6774,7 @@
         <v>301</v>
       </c>
       <c r="F240">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G240">
         <v>1560</v>
@@ -6804,7 +6800,7 @@
         <v>443</v>
       </c>
       <c r="F241">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G241">
         <v>1680</v>
@@ -6830,7 +6826,7 @@
         <v>378</v>
       </c>
       <c r="F242">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G242">
         <v>2868</v>
@@ -6856,7 +6852,7 @@
         <v>341</v>
       </c>
       <c r="F243">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G243">
         <v>2868</v>
@@ -6882,7 +6878,7 @@
         <v>334</v>
       </c>
       <c r="F244">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G244">
         <v>2868</v>
@@ -6908,7 +6904,7 @@
         <v>199</v>
       </c>
       <c r="F245">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G245">
         <v>2868</v>
@@ -6934,7 +6930,7 @@
         <v>483</v>
       </c>
       <c r="F246">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G246">
         <v>2868</v>
@@ -6960,7 +6956,7 @@
         <v>530</v>
       </c>
       <c r="F247">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G247">
         <v>2868</v>
@@ -6986,7 +6982,7 @@
         <v>232</v>
       </c>
       <c r="F248">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G248">
         <v>2868</v>
@@ -7012,7 +7008,7 @@
         <v>317</v>
       </c>
       <c r="F249">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G249">
         <v>2868</v>
@@ -7038,7 +7034,7 @@
         <v>373</v>
       </c>
       <c r="F250">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G250">
         <v>2868</v>
@@ -7064,7 +7060,7 @@
         <v>418</v>
       </c>
       <c r="F251">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G251">
         <v>2868</v>
@@ -7090,7 +7086,7 @@
         <v>165</v>
       </c>
       <c r="F252">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G252">
         <v>2868</v>
@@ -7116,7 +7112,7 @@
         <v>404</v>
       </c>
       <c r="F253">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G253">
         <v>2868</v>
@@ -7142,7 +7138,7 @@
         <v>522</v>
       </c>
       <c r="F254">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G254">
         <v>5340</v>
@@ -7168,7 +7164,7 @@
         <v>233</v>
       </c>
       <c r="F255">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G255">
         <v>3288</v>
@@ -7194,7 +7190,7 @@
         <v>204</v>
       </c>
       <c r="F256">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G256">
         <v>4056</v>
@@ -7220,7 +7216,7 @@
         <v>380</v>
       </c>
       <c r="F257">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G257">
         <v>5412</v>
@@ -7246,7 +7242,7 @@
         <v>231</v>
       </c>
       <c r="F258">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G258">
         <v>2196</v>
@@ -7272,7 +7268,7 @@
         <v>322</v>
       </c>
       <c r="F259">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G259">
         <v>3732</v>
@@ -7298,7 +7294,7 @@
         <v>307</v>
       </c>
       <c r="F260">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G260">
         <v>4380</v>
@@ -7324,7 +7320,7 @@
         <v>301</v>
       </c>
       <c r="F261">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G261">
         <v>4932</v>
@@ -7350,7 +7346,7 @@
         <v>216</v>
       </c>
       <c r="F262">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G262">
         <v>1560</v>
@@ -7376,7 +7372,7 @@
         <v>591</v>
       </c>
       <c r="F263">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G263">
         <v>828</v>
@@ -7402,7 +7398,7 @@
         <v>472</v>
       </c>
       <c r="F264">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G264">
         <v>4692</v>
@@ -7428,7 +7424,7 @@
         <v>505</v>
       </c>
       <c r="F265">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G265">
         <v>5700</v>
@@ -7454,7 +7450,7 @@
         <v>494</v>
       </c>
       <c r="F266">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G266">
         <v>4632</v>
@@ -7480,7 +7476,7 @@
         <v>503</v>
       </c>
       <c r="F267">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G267">
         <v>4140</v>
@@ -7506,7 +7502,7 @@
         <v>558</v>
       </c>
       <c r="F268">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G268">
         <v>684</v>
@@ -7532,7 +7528,7 @@
         <v>511</v>
       </c>
       <c r="F269">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G269">
         <v>5868</v>
@@ -7558,7 +7554,7 @@
         <v>305</v>
       </c>
       <c r="F270">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G270">
         <v>1056</v>
@@ -7584,7 +7580,7 @@
         <v>324</v>
       </c>
       <c r="F271">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G271">
         <v>5004</v>
@@ -7610,7 +7606,7 @@
         <v>395</v>
       </c>
       <c r="F272">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G272">
         <v>5244</v>
@@ -7636,7 +7632,7 @@
         <v>251</v>
       </c>
       <c r="F273">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G273">
         <v>2988</v>
@@ -7662,7 +7658,7 @@
         <v>592</v>
       </c>
       <c r="F274">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G274">
         <v>1032</v>
@@ -7688,7 +7684,7 @@
         <v>409</v>
       </c>
       <c r="F275">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G275">
         <v>2292</v>
@@ -7714,7 +7710,7 @@
         <v>470</v>
       </c>
       <c r="F276">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G276">
         <v>3576</v>
@@ -7740,7 +7736,7 @@
         <v>248</v>
       </c>
       <c r="F277">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G277">
         <v>2820</v>
@@ -7766,7 +7762,7 @@
         <v>548</v>
       </c>
       <c r="F278">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G278">
         <v>2414</v>
@@ -7792,7 +7788,7 @@
         <v>168</v>
       </c>
       <c r="F279">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G279">
         <v>2414</v>
@@ -7818,7 +7814,7 @@
         <v>476</v>
       </c>
       <c r="F280">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G280">
         <v>2414</v>
@@ -7844,7 +7840,7 @@
         <v>495</v>
       </c>
       <c r="F281">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G281">
         <v>2414</v>
@@ -7870,7 +7866,7 @@
         <v>490</v>
       </c>
       <c r="F282">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G282">
         <v>2414</v>
@@ -7896,7 +7892,7 @@
         <v>284</v>
       </c>
       <c r="F283">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G283">
         <v>2414</v>
@@ -7922,7 +7918,7 @@
         <v>466</v>
       </c>
       <c r="F284">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G284">
         <v>2414</v>
@@ -7948,7 +7944,7 @@
         <v>299</v>
       </c>
       <c r="F285">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G285">
         <v>2414</v>
@@ -7974,7 +7970,7 @@
         <v>385</v>
       </c>
       <c r="F286">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G286">
         <v>2414</v>
@@ -8000,7 +7996,7 @@
         <v>424</v>
       </c>
       <c r="F287">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G287">
         <v>2414</v>
@@ -8026,7 +8022,7 @@
         <v>377</v>
       </c>
       <c r="F288">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G288">
         <v>2414</v>
@@ -8052,7 +8048,7 @@
         <v>472</v>
       </c>
       <c r="F289">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G289">
         <v>2414</v>
@@ -8078,7 +8074,7 @@
         <v>372</v>
       </c>
       <c r="F290">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G290">
         <v>2544</v>
@@ -8104,7 +8100,7 @@
         <v>261</v>
       </c>
       <c r="F291">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G291">
         <v>5484</v>
@@ -8130,7 +8126,7 @@
         <v>324</v>
       </c>
       <c r="F292">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G292">
         <v>2436</v>
@@ -8156,7 +8152,7 @@
         <v>231</v>
       </c>
       <c r="F293">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G293">
         <v>2964</v>
@@ -8182,7 +8178,7 @@
         <v>233</v>
       </c>
       <c r="F294">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G294">
         <v>1356</v>
@@ -8208,7 +8204,7 @@
         <v>377</v>
       </c>
       <c r="F295">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G295">
         <v>1284</v>
@@ -8234,7 +8230,7 @@
         <v>511</v>
       </c>
       <c r="F296">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G296">
         <v>4056</v>
@@ -8260,7 +8256,7 @@
         <v>583</v>
       </c>
       <c r="F297">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G297">
         <v>3108</v>
@@ -8286,7 +8282,7 @@
         <v>338</v>
       </c>
       <c r="F298">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G298">
         <v>5160</v>
@@ -8312,7 +8308,7 @@
         <v>251</v>
       </c>
       <c r="F299">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G299">
         <v>3948</v>
@@ -8338,7 +8334,7 @@
         <v>493</v>
       </c>
       <c r="F300">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G300">
         <v>4428</v>
@@ -8364,7 +8360,7 @@
         <v>435</v>
       </c>
       <c r="F301">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G301">
         <v>3144</v>
@@ -8390,7 +8386,7 @@
         <v>591</v>
       </c>
       <c r="F302">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G302">
         <v>3036</v>
@@ -8416,7 +8412,7 @@
         <v>474</v>
       </c>
       <c r="F303">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G303">
         <v>3084</v>
@@ -8442,7 +8438,7 @@
         <v>390</v>
       </c>
       <c r="F304">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G304">
         <v>5352</v>
@@ -8468,7 +8464,7 @@
         <v>539</v>
       </c>
       <c r="F305">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G305">
         <v>3240</v>
@@ -8494,7 +8490,7 @@
         <v>449</v>
       </c>
       <c r="F306">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G306">
         <v>5832</v>
@@ -8520,7 +8516,7 @@
         <v>540</v>
       </c>
       <c r="F307">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G307">
         <v>5808</v>
@@ -8546,7 +8542,7 @@
         <v>474</v>
       </c>
       <c r="F308">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G308">
         <v>3324</v>
@@ -8572,7 +8568,7 @@
         <v>381</v>
       </c>
       <c r="F309">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G309">
         <v>3576</v>
@@ -8598,7 +8594,7 @@
         <v>286</v>
       </c>
       <c r="F310">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G310">
         <v>1776</v>
@@ -8624,7 +8620,7 @@
         <v>271</v>
       </c>
       <c r="F311">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G311">
         <v>2616</v>
@@ -8650,7 +8646,7 @@
         <v>277</v>
       </c>
       <c r="F312">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G312">
         <v>3036</v>
@@ -8676,7 +8672,7 @@
         <v>499</v>
       </c>
       <c r="F313">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G313">
         <v>3192</v>
@@ -8702,7 +8698,7 @@
         <v>316</v>
       </c>
       <c r="F314">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G314">
         <v>2653</v>
@@ -8728,7 +8724,7 @@
         <v>282</v>
       </c>
       <c r="F315">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G315">
         <v>2653</v>
@@ -8754,7 +8750,7 @@
         <v>309</v>
       </c>
       <c r="F316">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G316">
         <v>2653</v>
@@ -8780,7 +8776,7 @@
         <v>489</v>
       </c>
       <c r="F317">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G317">
         <v>2653</v>
@@ -8806,7 +8802,7 @@
         <v>325</v>
       </c>
       <c r="F318">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G318">
         <v>2653</v>
@@ -8832,7 +8828,7 @@
         <v>517</v>
       </c>
       <c r="F319">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G319">
         <v>2653</v>
@@ -8858,7 +8854,7 @@
         <v>477</v>
       </c>
       <c r="F320">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G320">
         <v>2653</v>
@@ -8884,7 +8880,7 @@
         <v>366</v>
       </c>
       <c r="F321">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G321">
         <v>2653</v>
@@ -8910,7 +8906,7 @@
         <v>555</v>
       </c>
       <c r="F322">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G322">
         <v>2653</v>
@@ -8936,7 +8932,7 @@
         <v>301</v>
       </c>
       <c r="F323">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G323">
         <v>2653</v>
@@ -8962,7 +8958,7 @@
         <v>174</v>
       </c>
       <c r="F324">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G324">
         <v>2653</v>
@@ -8988,7 +8984,7 @@
         <v>362</v>
       </c>
       <c r="F325">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G325">
         <v>2653</v>
@@ -9014,7 +9010,7 @@
         <v>566</v>
       </c>
       <c r="F326">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G326">
         <v>2100</v>
@@ -9040,7 +9036,7 @@
         <v>493</v>
       </c>
       <c r="F327">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G327">
         <v>3996</v>
@@ -9066,7 +9062,7 @@
         <v>581</v>
       </c>
       <c r="F328">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G328">
         <v>5304</v>
@@ -9092,7 +9088,7 @@
         <v>425</v>
       </c>
       <c r="F329">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G329">
         <v>1572</v>
@@ -9118,7 +9114,7 @@
         <v>484</v>
       </c>
       <c r="F330">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G330">
         <v>3300</v>
@@ -9144,7 +9140,7 @@
         <v>416</v>
       </c>
       <c r="F331">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G331">
         <v>2040</v>
@@ -9170,7 +9166,7 @@
         <v>258</v>
       </c>
       <c r="F332">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G332">
         <v>1128</v>
@@ -9196,7 +9192,7 @@
         <v>244</v>
       </c>
       <c r="F333">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G333">
         <v>672</v>
@@ -9222,7 +9218,7 @@
         <v>343</v>
       </c>
       <c r="F334">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G334">
         <v>3564</v>
@@ -9248,7 +9244,7 @@
         <v>368</v>
       </c>
       <c r="F335">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G335">
         <v>4668</v>
@@ -9274,7 +9270,7 @@
         <v>344</v>
       </c>
       <c r="F336">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G336">
         <v>1056</v>
@@ -9300,7 +9296,7 @@
         <v>519</v>
       </c>
       <c r="F337">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G337">
         <v>1212</v>
@@ -9326,7 +9322,7 @@
         <v>384</v>
       </c>
       <c r="F338">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G338">
         <v>2844</v>
@@ -9352,7 +9348,7 @@
         <v>330</v>
       </c>
       <c r="F339">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G339">
         <v>3012</v>
@@ -9378,7 +9374,7 @@
         <v>376</v>
       </c>
       <c r="F340">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G340">
         <v>744</v>
@@ -9404,7 +9400,7 @@
         <v>337</v>
       </c>
       <c r="F341">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G341">
         <v>1728</v>
@@ -9430,7 +9426,7 @@
         <v>400</v>
       </c>
       <c r="F342">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G342">
         <v>2160</v>
@@ -9456,7 +9452,7 @@
         <v>556</v>
       </c>
       <c r="F343">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G343">
         <v>4296</v>
@@ -9482,7 +9478,7 @@
         <v>531</v>
       </c>
       <c r="F344">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G344">
         <v>5424</v>
@@ -9508,7 +9504,7 @@
         <v>256</v>
       </c>
       <c r="F345">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G345">
         <v>1452</v>
@@ -9534,7 +9530,7 @@
         <v>262</v>
       </c>
       <c r="F346">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G346">
         <v>4248</v>
@@ -9560,7 +9556,7 @@
         <v>594</v>
       </c>
       <c r="F347">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G347">
         <v>1812</v>
@@ -9586,7 +9582,7 @@
         <v>350</v>
       </c>
       <c r="F348">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G348">
         <v>3240</v>
@@ -9612,7 +9608,7 @@
         <v>264</v>
       </c>
       <c r="F349">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G349">
         <v>4332</v>
@@ -9638,7 +9634,7 @@
         <v>434</v>
       </c>
       <c r="F350">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G350">
         <v>2680</v>
@@ -9664,7 +9660,7 @@
         <v>334</v>
       </c>
       <c r="F351">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G351">
         <v>2680</v>
@@ -9690,7 +9686,7 @@
         <v>324</v>
       </c>
       <c r="F352">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G352">
         <v>2680</v>
@@ -9716,7 +9712,7 @@
         <v>473</v>
       </c>
       <c r="F353">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G353">
         <v>2680</v>
@@ -9742,7 +9738,7 @@
         <v>356</v>
       </c>
       <c r="F354">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G354">
         <v>2680</v>
@@ -9768,7 +9764,7 @@
         <v>341</v>
       </c>
       <c r="F355">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G355">
         <v>2680</v>
@@ -9794,7 +9790,7 @@
         <v>488</v>
       </c>
       <c r="F356">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G356">
         <v>2680</v>
@@ -9820,7 +9816,7 @@
         <v>396</v>
       </c>
       <c r="F357">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G357">
         <v>2680</v>
@@ -9846,7 +9842,7 @@
         <v>360</v>
       </c>
       <c r="F358">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G358">
         <v>2680</v>
@@ -9872,7 +9868,7 @@
         <v>343</v>
       </c>
       <c r="F359">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G359">
         <v>2680</v>
@@ -9898,7 +9894,7 @@
         <v>270</v>
       </c>
       <c r="F360">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G360">
         <v>2680</v>
@@ -9924,7 +9920,7 @@
         <v>415</v>
       </c>
       <c r="F361">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G361">
         <v>2680</v>
@@ -9950,7 +9946,7 @@
         <v>290</v>
       </c>
       <c r="F362">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G362">
         <v>5964</v>
@@ -9976,7 +9972,7 @@
         <v>409</v>
       </c>
       <c r="F363">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G363">
         <v>4464</v>
@@ -10002,7 +9998,7 @@
         <v>369</v>
       </c>
       <c r="F364">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G364">
         <v>4524</v>
@@ -10028,7 +10024,7 @@
         <v>233</v>
       </c>
       <c r="F365">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G365">
         <v>5400</v>
@@ -10054,7 +10050,7 @@
         <v>368</v>
       </c>
       <c r="F366">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G366">
         <v>4572</v>
@@ -10080,7 +10076,7 @@
         <v>495</v>
       </c>
       <c r="F367">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G367">
         <v>1584</v>
@@ -10106,7 +10102,7 @@
         <v>446</v>
       </c>
       <c r="F368">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G368">
         <v>1920</v>
@@ -10132,7 +10128,7 @@
         <v>306</v>
       </c>
       <c r="F369">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G369">
         <v>960</v>
@@ -10158,7 +10154,7 @@
         <v>245</v>
       </c>
       <c r="F370">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G370">
         <v>1488</v>
@@ -10184,7 +10180,7 @@
         <v>238</v>
       </c>
       <c r="F371">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G371">
         <v>5616</v>
@@ -10210,7 +10206,7 @@
         <v>537</v>
       </c>
       <c r="F372">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G372">
         <v>1572</v>
@@ -10236,7 +10232,7 @@
         <v>200</v>
       </c>
       <c r="F373">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G373">
         <v>2052</v>
@@ -10262,7 +10258,7 @@
         <v>549</v>
       </c>
       <c r="F374">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G374">
         <v>5640</v>
@@ -10288,7 +10284,7 @@
         <v>210</v>
       </c>
       <c r="F375">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G375">
         <v>5076</v>
@@ -10314,7 +10310,7 @@
         <v>288</v>
       </c>
       <c r="F376">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G376">
         <v>4704</v>
@@ -10340,7 +10336,7 @@
         <v>202</v>
       </c>
       <c r="F377">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G377">
         <v>3960</v>
@@ -10366,7 +10362,7 @@
         <v>233</v>
       </c>
       <c r="F378">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G378">
         <v>3444</v>
@@ -10392,7 +10388,7 @@
         <v>241</v>
       </c>
       <c r="F379">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G379">
         <v>2052</v>
@@ -10418,7 +10414,7 @@
         <v>337</v>
       </c>
       <c r="F380">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G380">
         <v>5640</v>
@@ -10444,7 +10440,7 @@
         <v>237</v>
       </c>
       <c r="F381">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G381">
         <v>4140</v>
@@ -10470,7 +10466,7 @@
         <v>239</v>
       </c>
       <c r="F382">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G382">
         <v>936</v>
@@ -10496,7 +10492,7 @@
         <v>353</v>
       </c>
       <c r="F383">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G383">
         <v>4668</v>
@@ -10522,7 +10518,7 @@
         <v>303</v>
       </c>
       <c r="F384">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G384">
         <v>1548</v>
@@ -10548,7 +10544,7 @@
         <v>262</v>
       </c>
       <c r="F385">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G385">
         <v>5388</v>
@@ -10574,7 +10570,7 @@
         <v>387</v>
       </c>
       <c r="F386">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G386">
         <v>2507</v>
@@ -10600,7 +10596,7 @@
         <v>277</v>
       </c>
       <c r="F387">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G387">
         <v>2507</v>
@@ -10626,7 +10622,7 @@
         <v>273</v>
       </c>
       <c r="F388">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G388">
         <v>2507</v>
@@ -10652,7 +10648,7 @@
         <v>304</v>
       </c>
       <c r="F389">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G389">
         <v>2507</v>
@@ -10678,7 +10674,7 @@
         <v>337</v>
       </c>
       <c r="F390">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G390">
         <v>2507</v>
@@ -10704,7 +10700,7 @@
         <v>176</v>
       </c>
       <c r="F391">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G391">
         <v>2507</v>
@@ -10730,7 +10726,7 @@
         <v>197</v>
       </c>
       <c r="F392">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G392">
         <v>2507</v>
@@ -10756,7 +10752,7 @@
         <v>449</v>
       </c>
       <c r="F393">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G393">
         <v>2507</v>
@@ -10782,7 +10778,7 @@
         <v>419</v>
       </c>
       <c r="F394">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G394">
         <v>2507</v>
@@ -10808,7 +10804,7 @@
         <v>228</v>
       </c>
       <c r="F395">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G395">
         <v>2507</v>
@@ -10834,7 +10830,7 @@
         <v>518</v>
       </c>
       <c r="F396">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G396">
         <v>2507</v>
@@ -10860,7 +10856,7 @@
         <v>250</v>
       </c>
       <c r="F397">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G397">
         <v>2507</v>
@@ -10886,7 +10882,7 @@
         <v>374</v>
       </c>
       <c r="F398">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G398">
         <v>5052</v>
@@ -10912,7 +10908,7 @@
         <v>301</v>
       </c>
       <c r="F399">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G399">
         <v>1188</v>
@@ -10938,7 +10934,7 @@
         <v>201</v>
       </c>
       <c r="F400">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G400">
         <v>5688</v>
@@ -10964,7 +10960,7 @@
         <v>202</v>
       </c>
       <c r="F401">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G401">
         <v>4776</v>
@@ -10990,7 +10986,7 @@
         <v>521</v>
       </c>
       <c r="F402">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G402">
         <v>1764</v>
@@ -11016,7 +11012,7 @@
         <v>397</v>
       </c>
       <c r="F403">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G403">
         <v>5316</v>
@@ -11042,7 +11038,7 @@
         <v>378</v>
       </c>
       <c r="F404">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G404">
         <v>3108</v>
@@ -11068,7 +11064,7 @@
         <v>308</v>
       </c>
       <c r="F405">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G405">
         <v>3168</v>
@@ -11094,7 +11090,7 @@
         <v>305</v>
       </c>
       <c r="F406">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G406">
         <v>5400</v>
@@ -11120,7 +11116,7 @@
         <v>513</v>
       </c>
       <c r="F407">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G407">
         <v>5880</v>
@@ -11146,7 +11142,7 @@
         <v>253</v>
       </c>
       <c r="F408">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G408">
         <v>5484</v>
@@ -11172,7 +11168,7 @@
         <v>473</v>
       </c>
       <c r="F409">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G409">
         <v>5772</v>
@@ -11198,7 +11194,7 @@
         <v>579</v>
       </c>
       <c r="F410">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G410">
         <v>5424</v>
@@ -11224,7 +11220,7 @@
         <v>546</v>
       </c>
       <c r="F411">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G411">
         <v>2328</v>
@@ -11250,7 +11246,7 @@
         <v>240</v>
       </c>
       <c r="F412">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G412">
         <v>4788</v>
@@ -11276,7 +11272,7 @@
         <v>427</v>
       </c>
       <c r="F413">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G413">
         <v>3168</v>
@@ -11302,7 +11298,7 @@
         <v>552</v>
       </c>
       <c r="F414">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G414">
         <v>1308</v>
@@ -11328,7 +11324,7 @@
         <v>287</v>
       </c>
       <c r="F415">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G415">
         <v>5244</v>
@@ -11354,7 +11350,7 @@
         <v>337</v>
       </c>
       <c r="F416">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G416">
         <v>5364</v>
@@ -11380,7 +11376,7 @@
         <v>454</v>
       </c>
       <c r="F417">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G417">
         <v>5052</v>
@@ -11406,7 +11402,7 @@
         <v>534</v>
       </c>
       <c r="F418">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G418">
         <v>960</v>
@@ -11432,7 +11428,7 @@
         <v>284</v>
       </c>
       <c r="F419">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G419">
         <v>5916</v>
@@ -11458,7 +11454,7 @@
         <v>284</v>
       </c>
       <c r="F420">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G420">
         <v>1260</v>
@@ -11484,7 +11480,7 @@
         <v>344</v>
       </c>
       <c r="F421">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G421">
         <v>5184</v>
@@ -11510,7 +11506,7 @@
         <v>305</v>
       </c>
       <c r="F422">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G422">
         <v>3109</v>
@@ -11536,7 +11532,7 @@
         <v>383</v>
       </c>
       <c r="F423">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G423">
         <v>3109</v>
@@ -11562,7 +11558,7 @@
         <v>139</v>
       </c>
       <c r="F424">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G424">
         <v>3109</v>
@@ -11588,7 +11584,7 @@
         <v>303</v>
       </c>
       <c r="F425">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G425">
         <v>3109</v>
@@ -11614,7 +11610,7 @@
         <v>396</v>
       </c>
       <c r="F426">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G426">
         <v>3109</v>
@@ -11640,7 +11636,7 @@
         <v>408</v>
       </c>
       <c r="F427">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G427">
         <v>3109</v>
@@ -11666,7 +11662,7 @@
         <v>343</v>
       </c>
       <c r="F428">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G428">
         <v>3109</v>
@@ -11692,7 +11688,7 @@
         <v>398</v>
       </c>
       <c r="F429">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G429">
         <v>3109</v>
@@ -11718,7 +11714,7 @@
         <v>465</v>
       </c>
       <c r="F430">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G430">
         <v>3109</v>
@@ -11744,7 +11740,7 @@
         <v>345</v>
       </c>
       <c r="F431">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G431">
         <v>3109</v>
@@ -11770,7 +11766,7 @@
         <v>370</v>
       </c>
       <c r="F432">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G432">
         <v>3109</v>
@@ -11796,7 +11792,7 @@
         <v>198</v>
       </c>
       <c r="F433">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G433">
         <v>3109</v>
@@ -11822,7 +11818,7 @@
         <v>490</v>
       </c>
       <c r="F434">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G434">
         <v>4944</v>
@@ -11848,7 +11844,7 @@
         <v>476</v>
       </c>
       <c r="F435">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G435">
         <v>1008</v>
@@ -11874,7 +11870,7 @@
         <v>378</v>
       </c>
       <c r="F436">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G436">
         <v>3708</v>
@@ -11900,7 +11896,7 @@
         <v>323</v>
       </c>
       <c r="F437">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G437">
         <v>1536</v>
@@ -11926,7 +11922,7 @@
         <v>304</v>
       </c>
       <c r="F438">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G438">
         <v>2628</v>
@@ -11952,7 +11948,7 @@
         <v>282</v>
       </c>
       <c r="F439">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G439">
         <v>1188</v>
@@ -11978,7 +11974,7 @@
         <v>589</v>
       </c>
       <c r="F440">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G440">
         <v>2124</v>
@@ -12004,7 +12000,7 @@
         <v>587</v>
       </c>
       <c r="F441">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G441">
         <v>4560</v>
@@ -12030,7 +12026,7 @@
         <v>580</v>
       </c>
       <c r="F442">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G442">
         <v>5568</v>
@@ -12056,7 +12052,7 @@
         <v>265</v>
       </c>
       <c r="F443">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G443">
         <v>5520</v>
@@ -12082,7 +12078,7 @@
         <v>442</v>
       </c>
       <c r="F444">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G444">
         <v>3588</v>
@@ -12108,7 +12104,7 @@
         <v>402</v>
       </c>
       <c r="F445">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G445">
         <v>2916</v>
@@ -12134,7 +12130,7 @@
         <v>524</v>
       </c>
       <c r="F446">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G446">
         <v>1848</v>
@@ -12160,7 +12156,7 @@
         <v>512</v>
       </c>
       <c r="F447">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G447">
         <v>2868</v>
@@ -12186,7 +12182,7 @@
         <v>315</v>
       </c>
       <c r="F448">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G448">
         <v>4920</v>
@@ -12212,7 +12208,7 @@
         <v>294</v>
       </c>
       <c r="F449">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G449">
         <v>3276</v>
@@ -12238,7 +12234,7 @@
         <v>469</v>
       </c>
       <c r="F450">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G450">
         <v>1080</v>
@@ -12264,7 +12260,7 @@
         <v>441</v>
       </c>
       <c r="F451">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G451">
         <v>4884</v>
@@ -12290,7 +12286,7 @@
         <v>557</v>
       </c>
       <c r="F452">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G452">
         <v>3612</v>
@@ -12316,7 +12312,7 @@
         <v>414</v>
       </c>
       <c r="F453">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G453">
         <v>2172</v>
@@ -12342,7 +12338,7 @@
         <v>357</v>
       </c>
       <c r="F454">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G454">
         <v>2232</v>
@@ -12368,7 +12364,7 @@
         <v>446</v>
       </c>
       <c r="F455">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G455">
         <v>5088</v>
@@ -12394,7 +12390,7 @@
         <v>281</v>
       </c>
       <c r="F456">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G456">
         <v>3216</v>
@@ -12420,7 +12416,7 @@
         <v>256</v>
       </c>
       <c r="F457">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G457">
         <v>3324</v>
@@ -12446,7 +12442,7 @@
         <v>369</v>
       </c>
       <c r="F458">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G458">
         <v>2497</v>
@@ -12472,7 +12468,7 @@
         <v>417</v>
       </c>
       <c r="F459">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G459">
         <v>2497</v>
@@ -12498,7 +12494,7 @@
         <v>362</v>
       </c>
       <c r="F460">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G460">
         <v>2497</v>
@@ -12524,7 +12520,7 @@
         <v>332</v>
       </c>
       <c r="F461">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G461">
         <v>2497</v>
@@ -12550,7 +12546,7 @@
         <v>187</v>
       </c>
       <c r="F462">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G462">
         <v>2497</v>
@@ -12576,7 +12572,7 @@
         <v>143</v>
       </c>
       <c r="F463">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G463">
         <v>2497</v>
@@ -12602,7 +12598,7 @@
         <v>540</v>
       </c>
       <c r="F464">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G464">
         <v>2497</v>
@@ -12628,7 +12624,7 @@
         <v>334</v>
       </c>
       <c r="F465">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G465">
         <v>2497</v>
@@ -12654,7 +12650,7 @@
         <v>391</v>
       </c>
       <c r="F466">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G466">
         <v>2497</v>
@@ -12680,7 +12676,7 @@
         <v>552</v>
       </c>
       <c r="F467">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G467">
         <v>2497</v>
@@ -12706,7 +12702,7 @@
         <v>161</v>
       </c>
       <c r="F468">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G468">
         <v>2497</v>
@@ -12732,7 +12728,7 @@
         <v>537</v>
       </c>
       <c r="F469">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G469">
         <v>2497</v>
@@ -12758,7 +12754,7 @@
         <v>202</v>
       </c>
       <c r="F470">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G470">
         <v>1272</v>
@@ -12784,7 +12780,7 @@
         <v>509</v>
       </c>
       <c r="F471">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G471">
         <v>636</v>
@@ -12810,7 +12806,7 @@
         <v>514</v>
       </c>
       <c r="F472">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G472">
         <v>960</v>
@@ -12836,7 +12832,7 @@
         <v>529</v>
       </c>
       <c r="F473">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G473">
         <v>1104</v>
@@ -12862,7 +12858,7 @@
         <v>551</v>
       </c>
       <c r="F474">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G474">
         <v>1752</v>
@@ -12888,7 +12884,7 @@
         <v>515</v>
       </c>
       <c r="F475">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G475">
         <v>5580</v>
@@ -12914,7 +12910,7 @@
         <v>438</v>
       </c>
       <c r="F476">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G476">
         <v>4332</v>
@@ -12940,7 +12936,7 @@
         <v>482</v>
       </c>
       <c r="F477">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G477">
         <v>5040</v>
@@ -12966,7 +12962,7 @@
         <v>278</v>
       </c>
       <c r="F478">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G478">
         <v>5652</v>
@@ -12992,7 +12988,7 @@
         <v>528</v>
       </c>
       <c r="F479">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G479">
         <v>2088</v>
@@ -13018,7 +13014,7 @@
         <v>384</v>
       </c>
       <c r="F480">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G480">
         <v>1140</v>
@@ -13044,7 +13040,7 @@
         <v>525</v>
       </c>
       <c r="F481">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G481">
         <v>3660</v>
@@ -13070,7 +13066,7 @@
         <v>371</v>
       </c>
       <c r="F482">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G482">
         <v>5580</v>
@@ -13096,7 +13092,7 @@
         <v>524</v>
       </c>
       <c r="F483">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G483">
         <v>5016</v>
@@ -13122,7 +13118,7 @@
         <v>558</v>
       </c>
       <c r="F484">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G484">
         <v>5736</v>
@@ -13148,7 +13144,7 @@
         <v>599</v>
       </c>
       <c r="F485">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G485">
         <v>5208</v>
@@ -13174,7 +13170,7 @@
         <v>287</v>
       </c>
       <c r="F486">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G486">
         <v>5508</v>
@@ -13200,7 +13196,7 @@
         <v>296</v>
       </c>
       <c r="F487">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G487">
         <v>1188</v>
@@ -13226,7 +13222,7 @@
         <v>252</v>
       </c>
       <c r="F488">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G488">
         <v>1248</v>
@@ -13252,7 +13248,7 @@
         <v>390</v>
       </c>
       <c r="F489">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G489">
         <v>1992</v>
@@ -13278,7 +13274,7 @@
         <v>289</v>
       </c>
       <c r="F490">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G490">
         <v>3324</v>
@@ -13304,7 +13300,7 @@
         <v>403</v>
       </c>
       <c r="F491">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G491">
         <v>3948</v>
@@ -13330,7 +13326,7 @@
         <v>225</v>
       </c>
       <c r="F492">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G492">
         <v>2316</v>
@@ -13356,7 +13352,7 @@
         <v>458</v>
       </c>
       <c r="F493">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G493">
         <v>840</v>
@@ -13382,7 +13378,7 @@
         <v>415</v>
       </c>
       <c r="F494">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G494">
         <v>2898</v>
@@ -13408,7 +13404,7 @@
         <v>396</v>
       </c>
       <c r="F495">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G495">
         <v>2898</v>
@@ -13434,7 +13430,7 @@
         <v>293</v>
       </c>
       <c r="F496">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G496">
         <v>2898</v>
@@ -13460,7 +13456,7 @@
         <v>396</v>
       </c>
       <c r="F497">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G497">
         <v>2898</v>
@@ -13486,7 +13482,7 @@
         <v>423</v>
       </c>
       <c r="F498">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G498">
         <v>2898</v>
@@ -13512,7 +13508,7 @@
         <v>152</v>
       </c>
       <c r="F499">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G499">
         <v>2898</v>
@@ -13538,7 +13534,7 @@
         <v>176</v>
       </c>
       <c r="F500">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G500">
         <v>2898</v>
@@ -13564,7 +13560,7 @@
         <v>145</v>
       </c>
       <c r="F501">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G501">
         <v>2898</v>
@@ -13590,7 +13586,7 @@
         <v>350</v>
       </c>
       <c r="F502">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G502">
         <v>2898</v>
@@ -13616,7 +13612,7 @@
         <v>373</v>
       </c>
       <c r="F503">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G503">
         <v>2898</v>
@@ -13642,7 +13638,7 @@
         <v>128</v>
       </c>
       <c r="F504">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G504">
         <v>2898</v>
@@ -13668,7 +13664,7 @@
         <v>320</v>
       </c>
       <c r="F505">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G505">
         <v>2898</v>
@@ -13694,7 +13690,7 @@
         <v>392</v>
       </c>
       <c r="F506">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G506">
         <v>3792</v>
@@ -13720,7 +13716,7 @@
         <v>437</v>
       </c>
       <c r="F507">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G507">
         <v>2652</v>
@@ -13746,7 +13742,7 @@
         <v>234</v>
       </c>
       <c r="F508">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G508">
         <v>3816</v>
@@ -13772,7 +13768,7 @@
         <v>440</v>
       </c>
       <c r="F509">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G509">
         <v>1764</v>
@@ -13798,7 +13794,7 @@
         <v>477</v>
       </c>
       <c r="F510">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G510">
         <v>4752</v>
@@ -13824,7 +13820,7 @@
         <v>442</v>
       </c>
       <c r="F511">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G511">
         <v>4908</v>
@@ -13850,7 +13846,7 @@
         <v>236</v>
       </c>
       <c r="F512">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G512">
         <v>3336</v>
@@ -13876,7 +13872,7 @@
         <v>352</v>
       </c>
       <c r="F513">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G513">
         <v>1236</v>
@@ -13902,7 +13898,7 @@
         <v>439</v>
       </c>
       <c r="F514">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G514">
         <v>5028</v>
@@ -13928,7 +13924,7 @@
         <v>509</v>
       </c>
       <c r="F515">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G515">
         <v>2916</v>
@@ -13954,7 +13950,7 @@
         <v>470</v>
       </c>
       <c r="F516">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G516">
         <v>3360</v>
@@ -13980,7 +13976,7 @@
         <v>566</v>
       </c>
       <c r="F517">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G517">
         <v>2472</v>
@@ -14006,7 +14002,7 @@
         <v>211</v>
       </c>
       <c r="F518">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G518">
         <v>1368</v>
@@ -14032,7 +14028,7 @@
         <v>303</v>
       </c>
       <c r="F519">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G519">
         <v>696</v>
@@ -14058,7 +14054,7 @@
         <v>379</v>
       </c>
       <c r="F520">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G520">
         <v>2376</v>
@@ -14084,7 +14080,7 @@
         <v>387</v>
       </c>
       <c r="F521">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G521">
         <v>1656</v>
@@ -14110,7 +14106,7 @@
         <v>520</v>
       </c>
       <c r="F522">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G522">
         <v>5004</v>
@@ -14136,7 +14132,7 @@
         <v>570</v>
       </c>
       <c r="F523">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G523">
         <v>1692</v>
@@ -14162,7 +14158,7 @@
         <v>553</v>
       </c>
       <c r="F524">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G524">
         <v>5472</v>
@@ -14188,7 +14184,7 @@
         <v>352</v>
       </c>
       <c r="F525">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G525">
         <v>3792</v>
@@ -14214,7 +14210,7 @@
         <v>438</v>
       </c>
       <c r="F526">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G526">
         <v>4284</v>
@@ -14240,7 +14236,7 @@
         <v>572</v>
       </c>
       <c r="F527">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G527">
         <v>1716</v>
@@ -14266,7 +14262,7 @@
         <v>502</v>
       </c>
       <c r="F528">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G528">
         <v>2124</v>
@@ -14292,7 +14288,7 @@
         <v>500</v>
       </c>
       <c r="F529">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G529">
         <v>2712</v>
@@ -14318,7 +14314,7 @@
         <v>208</v>
       </c>
       <c r="F530">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G530">
         <v>2451</v>
@@ -14344,7 +14340,7 @@
         <v>227</v>
       </c>
       <c r="F531">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G531">
         <v>2451</v>
@@ -14370,7 +14366,7 @@
         <v>235</v>
       </c>
       <c r="F532">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G532">
         <v>2451</v>
@@ -14396,7 +14392,7 @@
         <v>292</v>
       </c>
       <c r="F533">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G533">
         <v>2451</v>
@@ -14422,7 +14418,7 @@
         <v>523</v>
       </c>
       <c r="F534">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G534">
         <v>2451</v>
@@ -14448,7 +14444,7 @@
         <v>505</v>
       </c>
       <c r="F535">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G535">
         <v>2451</v>
@@ -14474,7 +14470,7 @@
         <v>349</v>
       </c>
       <c r="F536">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G536">
         <v>2451</v>
@@ -14500,7 +14496,7 @@
         <v>281</v>
       </c>
       <c r="F537">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G537">
         <v>2451</v>
@@ -14526,7 +14522,7 @@
         <v>415</v>
       </c>
       <c r="F538">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G538">
         <v>2451</v>
@@ -14552,7 +14548,7 @@
         <v>302</v>
       </c>
       <c r="F539">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G539">
         <v>2451</v>
@@ -14578,7 +14574,7 @@
         <v>242</v>
       </c>
       <c r="F540">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G540">
         <v>2451</v>
@@ -14604,7 +14600,7 @@
         <v>290</v>
       </c>
       <c r="F541">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="G541">
         <v>2451</v>

--- a/pages/Base_de_Donnees_Ventes.xlsx
+++ b/pages/Base_de_Donnees_Ventes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Demand_Forecasting_System-main\Demand_Forecasting_System-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\Demand_Forecasting_System-main\Demand_Forecasting_System-main\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -541,6 +541,7 @@
     <col min="1" max="1" width="20.3984375" customWidth="1"/>
     <col min="2" max="2" width="12.265625" customWidth="1"/>
     <col min="4" max="4" width="15.46484375" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -583,7 +584,7 @@
         <v>373</v>
       </c>
       <c r="E2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="F2">
         <v>2023</v>
